--- a/Metadata/language metadata.xlsx
+++ b/Metadata/language metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francesco\Desktop\KG project\KG-2025-26-UniTn-Project\Metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21E418D8-DB46-4E32-99FF-5EE2C9B28DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E65B968-9489-46F2-ADAA-B46E9F7599D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1B3ABEBE-3093-42A2-8FE5-3C137E779EBB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>KeyWords</t>
   </si>
@@ -99,6 +99,12 @@
   </si>
   <si>
     <t>education, schools, institutes, municipalities, territory, Trento</t>
+  </si>
+  <si>
+    <t>Reference Teleontology</t>
+  </si>
+  <si>
+    <t>https://github.com/FrancescoMagalini1/KG-2025-26-UniTn-Project/blob/main/Phase%202%20-%20Language%20Definition/language_teleontology.rdf</t>
   </si>
 </sst>
 </file>
@@ -482,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A195CB6-C430-41BF-8F2B-B353F3AC06D8}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.33203125" customWidth="1"/>
@@ -494,9 +500,10 @@
     <col min="9" max="9" width="15" customWidth="1"/>
     <col min="10" max="10" width="17.5546875" customWidth="1"/>
     <col min="11" max="11" width="11.77734375" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -530,8 +537,11 @@
       <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -564,6 +574,9 @@
       </c>
       <c r="K2" s="2" t="s">
         <v>3</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
